--- a/output/pdf_financials_xlsx/EMNT.xlsx
+++ b/output/pdf_financials_xlsx/EMNT.xlsx
@@ -1093,43 +1093,43 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.354029</v>
+        <v>-0.354029</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.20104</v>
+        <v>-0.20104</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.13675</v>
+        <v>-0.13675</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.146623</v>
+        <v>-0.146623</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.100576</v>
+        <v>-0.100576</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.113589</v>
+        <v>-0.113589</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.082008</v>
+        <v>-0.082008</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>1.272588</v>
+        <v>-1.272588</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>1.212855</v>
+        <v>-1.212855</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.510919</v>
+        <v>-1.510919</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.178086</v>
+        <v>-4.178086</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>0.848071</v>
+        <v>-0.848071</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.092595</v>
+        <v>-2.092595</v>
       </c>
     </row>
     <row r="17">
@@ -1329,43 +1329,43 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.354029</v>
+        <v>-0.354029</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.20104</v>
+        <v>-0.20104</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.13675</v>
+        <v>-0.13675</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.146623</v>
+        <v>-0.146623</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.100576</v>
+        <v>-0.100576</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.113589</v>
+        <v>-0.113589</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.082008</v>
+        <v>-0.082008</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.272588</v>
+        <v>-1.272588</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.212855</v>
+        <v>-1.212855</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.510919</v>
+        <v>-1.510919</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.178086</v>
+        <v>-4.178086</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>0.848071</v>
+        <v>-0.848071</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.092595</v>
+        <v>-2.092595</v>
       </c>
     </row>
     <row r="21">
@@ -1467,43 +1467,43 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.354029</v>
+        <v>-0.354029</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.20104</v>
+        <v>-0.20104</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.13675</v>
+        <v>-0.13675</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.146623</v>
+        <v>-0.146623</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.100576</v>
+        <v>-0.100576</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.113589</v>
+        <v>-0.113589</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.082008</v>
+        <v>-0.082008</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>1.272588</v>
+        <v>-1.272588</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>1.212855</v>
+        <v>-1.212855</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.510919</v>
+        <v>-1.510919</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.178086</v>
+        <v>-4.178086</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>0.848071</v>
+        <v>-0.848071</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.092595</v>
+        <v>-2.092595</v>
       </c>
     </row>
     <row r="24">
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-11.800967</v>
+        <v>11.800967</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-10.052</v>
+        <v>10.052</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1636,22 +1636,22 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-31.8147</v>
+        <v>31.8147</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-40.4285</v>
+        <v>40.4285</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-37.772975</v>
+        <v>37.772975</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-46.423178</v>
+        <v>46.423178</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-42.40355</v>
+        <v>42.40355</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-69.753167</v>
+        <v>69.753167</v>
       </c>
     </row>
     <row r="27">
@@ -1661,43 +1661,43 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.354029</v>
+        <v>-0.354029</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.20104</v>
+        <v>-0.20104</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.13675</v>
+        <v>-0.13675</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.146623</v>
+        <v>-0.146623</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.100576</v>
+        <v>-0.100576</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.113589</v>
+        <v>-0.113589</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.082008</v>
+        <v>-0.082008</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>1.272588</v>
+        <v>-1.272588</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>1.212855</v>
+        <v>-1.212855</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.510919</v>
+        <v>-1.510919</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>4.178086</v>
+        <v>-4.178086</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>0.848071</v>
+        <v>-0.848071</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.092595</v>
+        <v>-2.092595</v>
       </c>
     </row>
     <row r="28">
@@ -1753,43 +1753,43 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.354029</v>
+        <v>-0.354029</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.20104</v>
+        <v>-0.20104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.13675</v>
+        <v>-0.13675</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.146623</v>
+        <v>-0.146623</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.100576</v>
+        <v>-0.100576</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.113589</v>
+        <v>-0.113589</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.082008</v>
+        <v>-0.082008</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.272588</v>
+        <v>-1.272588</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>1.212855</v>
+        <v>-1.212855</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.510919</v>
+        <v>-1.510919</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>4.178086</v>
+        <v>-4.178086</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.848071</v>
+        <v>-0.848071</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.092595</v>
+        <v>-2.092595</v>
       </c>
     </row>
     <row r="30">
@@ -1871,43 +1871,43 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4768,43 +4768,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.135817</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.816483</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.056473</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.464818</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.60415</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.681452</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>2.359221</v>
       </c>
     </row>
     <row r="93">
@@ -5925,13 +5925,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.174364</v>
+        <v>0.157351</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0.050279</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>0.02</v>
@@ -5946,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>0.02728</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>0.186816</v>
       </c>
       <c r="K118" s="3" t="n">
         <v>0</v>
@@ -7596,7 +7596,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -8152,7 +8156,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -8549,7 +8557,11 @@
           <t>Share-based payment reserve (Note 8)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -9604,7 +9616,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9930,7 +9946,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.135817</v>
       </c>
@@ -11532,7 +11552,11 @@
           <t>Exploration and evaluation expenditures $</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -12399,7 +12423,11 @@
           <t>Exploration and evaluation expenditures – Mineral</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -13136,7 +13164,11 @@
           <t>Exploration and evaluation expenditures – Mineral</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>-0.017013</v>
       </c>
@@ -14111,43 +14143,43 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.354029</v>
+        <v>-0.354029</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.20104</v>
+        <v>-0.20104</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.13675</v>
+        <v>-0.13675</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.146623</v>
+        <v>-0.146623</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.100576</v>
+        <v>-0.100576</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>0.113589</v>
+        <v>-0.113589</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>0.082008</v>
+        <v>-0.082008</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>1.272588</v>
+        <v>-1.272588</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>1.212855</v>
+        <v>-1.212855</v>
       </c>
       <c r="N96" s="5" t="n">
-        <v>1.510919</v>
+        <v>-1.510919</v>
       </c>
       <c r="O96" s="5" t="n">
-        <v>4.178086</v>
+        <v>-4.178086</v>
       </c>
       <c r="P96" s="5" t="n">
-        <v>0.848071</v>
+        <v>-0.848071</v>
       </c>
       <c r="Q96" s="5" t="n">
-        <v>2.092595</v>
+        <v>-2.092595</v>
       </c>
     </row>
     <row r="97">

--- a/output/pdf_financials_xlsx/EMNT.xlsx
+++ b/output/pdf_financials_xlsx/EMNT.xlsx
@@ -1996,7 +1996,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.183687</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.04846</v>
@@ -2005,34 +2005,34 @@
         <v>0.111343</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.030742</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.04027</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.001163</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.697769</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.564945</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.16352</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.096416</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.207046</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.080821</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.027664</v>
       </c>
     </row>
     <row r="35">
@@ -2088,7 +2088,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.183687</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.04846</v>
@@ -2097,34 +2097,34 @@
         <v>0.111343</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.030742</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.04027</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.001163</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.697769</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.564945</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.16352</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.096416</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.207046</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.080821</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.027664</v>
       </c>
     </row>
     <row r="37">
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.183687</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0</v>
@@ -2649,34 +2649,34 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.030742</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.04027</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.001163</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.697769</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.608255</v>
+        <v>0.04331</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.54358</v>
+        <v>0.38006</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.604775</v>
+        <v>0.508359</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.294145</v>
+        <v>0.087099</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.196525</v>
+        <v>0.115704</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.186522</v>
+        <v>0.158858</v>
       </c>
     </row>
     <row r="49">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -13697,7 +13697,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -16151,7 +16151,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">

--- a/output/pdf_financials_xlsx/EMNT.xlsx
+++ b/output/pdf_financials_xlsx/EMNT.xlsx
@@ -3540,43 +3540,43 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.008226000000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.00924</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.009266999999999999</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.03887</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.105261</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.045781</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="68">
@@ -12593,7 +12593,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
